--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,10 +535,10 @@
         <v>-108.62</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>176.58</v>
+        <v>176.57</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>285.19</v>
+        <v>285.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,7 +535,7 @@
         <v>-108.62</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>176.57</v>
+        <v>176.58</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>285.2</v>
